--- a/docs/Electro-V2-ERD-columns.xlsx
+++ b/docs/Electro-V2-ERD-columns.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp2\htdocs\Electro-V2\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0131C0E4-FBAB-41E2-B30B-F2CD42920378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_3785F3B9D11383B585734B2CD0E927DD79FB1816" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="74">
   <si>
     <t>User</t>
   </si>
@@ -130,7 +130,7 @@
     <t>password (string)</t>
   </si>
   <si>
-    <t>description (text)</t>
+    <t>description_en (text) — English; shown when site language is EN</t>
   </si>
   <si>
     <t>status (enum) — pending,paid,shipped,delivered,canceled</t>
@@ -142,6 +142,9 @@
     <t>comment (text)</t>
   </si>
   <si>
+    <t>description_ar (text) — Arabic; shown when site language is AR</t>
+  </si>
+  <si>
     <t>phone (int) nullable</t>
   </si>
   <si>
@@ -187,9 +190,6 @@
     <t>Cardinality</t>
   </si>
   <si>
-    <t>FK column (on child)</t>
-  </si>
-  <si>
     <t>On delete</t>
   </si>
   <si>
@@ -205,18 +205,12 @@
     <t>1:N</t>
   </si>
   <si>
-    <t>category_id</t>
-  </si>
-  <si>
     <t>CASCADE</t>
   </si>
   <si>
     <t>brands</t>
   </si>
   <si>
-    <t>brand_id</t>
-  </si>
-  <si>
     <t>users</t>
   </si>
   <si>
@@ -226,46 +220,25 @@
     <t>1:1</t>
   </si>
   <si>
-    <t>user_id</t>
-  </si>
-  <si>
     <t>one cart per user</t>
   </si>
   <si>
     <t>cart_items</t>
   </si>
   <si>
-    <t>cart_id</t>
-  </si>
-  <si>
-    <t>product_id</t>
-  </si>
-  <si>
     <t>orders</t>
   </si>
   <si>
     <t>areas</t>
   </si>
   <si>
-    <t>area_id</t>
-  </si>
-  <si>
     <t>cities</t>
   </si>
   <si>
-    <t>city_id</t>
-  </si>
-  <si>
     <t>order_items</t>
   </si>
   <si>
-    <t>order_id</t>
-  </si>
-  <si>
     <t>order_logs</t>
-  </si>
-  <si>
-    <t>admin_id</t>
   </si>
   <si>
     <t>reviews</t>
@@ -275,7 +248,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,6 +282,10 @@
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -340,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -354,8 +331,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -658,13 +638,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -706,7 +686,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -748,7 +728,7 @@
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
     </row>
-    <row r="3" spans="1:16" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -832,7 +812,7 @@
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
     </row>
-    <row r="5" spans="1:16" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
@@ -873,11 +853,11 @@
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
     </row>
-    <row r="6" spans="1:16" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="6" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -902,152 +882,140 @@
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:16" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="D7" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="D8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="2" t="s">
+      <c r="I8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L7" s="2" t="s">
+      <c r="K8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" spans="1:16" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="D9" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P8" s="2"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>28</v>
       </c>
       <c r="P9" s="2"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>49</v>
+      <c r="I10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="P10" s="2"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="P11" s="2"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="P12" s="2"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B17" s="3" t="s">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="D18" s="3"/>
+      <c r="E18" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" s="2"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>59</v>
@@ -1055,238 +1023,220 @@
       <c r="C19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>68</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>69</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F20" s="2"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>72</v>
-      </c>
+      <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>68</v>
-      </c>
+      <c r="D23" s="2"/>
       <c r="E23" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>75</v>
-      </c>
+      <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>77</v>
-      </c>
+      <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F25" s="2"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>79</v>
-      </c>
+      <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F26" s="2"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>72</v>
-      </c>
+      <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F27" s="2"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>79</v>
-      </c>
+      <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F28" s="2"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>81</v>
-      </c>
+      <c r="D29" s="2"/>
       <c r="E29" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F29" s="2"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>68</v>
-      </c>
+      <c r="D30" s="2"/>
       <c r="E30" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F30" s="2"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>72</v>
-      </c>
+      <c r="D31" s="2"/>
       <c r="E31" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F31" s="2"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
+      <c r="A32" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
+      <c r="E32" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="F32" s="2"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -1297,13 +1247,24 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
     </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+    </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="6"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="2">
